--- a/шаблони/комплекти/Стрільби/Шаблон_Відомість складання заліку з вимог безпеки (Додаток 8).xlsx
+++ b/шаблони/комплекти/Стрільби/Шаблон_Відомість складання заліку з вимог безпеки (Додаток 8).xlsx
@@ -34,58 +34,58 @@
 </x:t>
   </x:si>
   <x:si>
+    <x:t>Військова частина : {{номер_вч}}</x:t>
+  </x:si>
+  <x:si>
     <x:t>Підрозділ : {{опис_підрозділу}}</x:t>
   </x:si>
   <x:si>
+    <x:t>№ з/п</x:t>
+  </x:si>
+  <x:si>
+    <x:t>посада</x:t>
+  </x:si>
+  <x:si>
+    <x:t>військове звання</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ПІБ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Дата (число, місяць, рік) складання заліку</x:t>
+  </x:si>
+  <x:si>
     <x:t>З якої причини проведено інструктаж</x:t>
   </x:si>
   <x:si>
-    <x:t>№ з/п</x:t>
-  </x:si>
-  <x:si>
-    <x:t>посада</x:t>
-  </x:si>
-  <x:si>
-    <x:t>військове звання</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ПІБ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Дата (число, місяць, рік) складання заліку</x:t>
+    <x:t>підпис того, хто отримав інструктаж</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Посада, військове звання, підпис, ініціали, прізвище особи, яка проводила інструктаж</x:t>
   </x:si>
   <x:si>
     <x:t>{{№}}</x:t>
   </x:si>
   <x:si>
-    <x:t>підпис того, хто отримав інструктаж</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Посада, військове звання, підпис, ініціали, прізвище особи, яка проводила інструктаж</x:t>
-  </x:si>
-  <x:si>
     <x:t>слухач</x:t>
   </x:si>
   <x:si>
+    <x:t>{{звання}}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{{піб}}</x:t>
   </x:si>
   <x:si>
     <x:t>{{дата_аркуша}}</x:t>
   </x:si>
   <x:si>
+    <x:t>{{причина_інструктажу}}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{{курсовий_офіцер}}</x:t>
   </x:si>
   <x:si>
-    <x:t>{{звання}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Військова частина : {{номер_вч}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{причина_інструктажу}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Начальник курсів перепідготовки та підвищення кваліфікації Харківського національного університету Повітряних Сил
+    <x:t xml:space="preserve">{{посада_підписанта}}
 {{звання_підписанта}}                                                                                   {{піб_підписанта}}
 {{дата_аркуша}} р.
 </x:t>
@@ -95,10 +95,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="164" formatCode="General"/>
     <x:numFmt numFmtId="165" formatCode="0"/>
     <x:numFmt numFmtId="166" formatCode="[$-409]m/d/yyyy"/>
+    <x:numFmt numFmtId="167" formatCode="dd.mm.yyyy"/>
   </x:numFmts>
   <x:fonts count="10">
     <x:font>
@@ -199,7 +200,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <x:protection locked="true" hidden="false"/>
@@ -251,8 +252,11 @@
     <x:xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="39">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <x:protection locked="true" hidden="false"/>
@@ -403,6 +407,10 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -595,7 +603,7 @@
     <x:row r="5" spans="1:257" ht="14.4" customHeight="1">
       <x:c r="A5" s="4"/>
       <x:c r="B5" s="36" t="s">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="36"/>
       <x:c r="D5" s="36"/>
@@ -608,7 +616,7 @@
     <x:row r="6" spans="1:257" ht="14.4" customHeight="1">
       <x:c r="A6" s="6"/>
       <x:c r="B6" s="36" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="36"/>
       <x:c r="D6" s="36"/>
@@ -647,7 +655,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G8" s="9" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H8" s="9" t="s">
         <x:v>10</x:v>
@@ -686,26 +694,26 @@
     <x:row r="10" spans="1:257" ht="45" customHeight="1">
       <x:c r="A10" s="6"/>
       <x:c r="B10" s="13" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C10" s="13" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F10" s="38" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="G10" s="18" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H10" s="13"/>
       <x:c r="I10" s="18" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:257" ht="99.6" customHeight="1">

--- a/шаблони/комплекти/Стрільби/Шаблон_Відомість складання заліку з вимог безпеки (Додаток 8).xlsx
+++ b/шаблони/комплекти/Стрільби/Шаблон_Відомість складання заліку з вимог безпеки (Додаток 8).xlsx
@@ -256,7 +256,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="40">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <x:protection locked="true" hidden="false"/>
@@ -411,6 +411,10 @@
     </x:xf>
     <x:xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -712,7 +716,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H10" s="13"/>
-      <x:c r="I10" s="18" t="s">
+      <x:c r="I10" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
